--- a/utils/monday_sprint_sprint_2023-24.xlsx
+++ b/utils/monday_sprint_sprint_2023-24.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="168">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -87,7 +87,7 @@
     <t>21/11/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>03/12/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -123,7 +123,10 @@
     <t>17/11/2023</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>02/12/2023</t>
+  </si>
+  <si>
+    <t>5555323953</t>
   </si>
   <si>
     <t>Consulta dos dados da movimentação do fluxo 109 para os dados da etapa 1 detalhando para cada linha do fluxo a pergunta feita e a resposta</t>
@@ -135,34 +138,43 @@
     <t>Semana 4</t>
   </si>
   <si>
+    <t>5555329964</t>
+  </si>
+  <si>
     <t>Desenvolvimento do fluxo 109 até a parte da avaliação de modelo (etapa 2)</t>
   </si>
   <si>
+    <t>30/11/2023</t>
+  </si>
+  <si>
+    <t>5555332619</t>
+  </si>
+  <si>
     <t>Testes com o usuário</t>
   </si>
   <si>
-    <t>23170</t>
+    <t>5532811009</t>
   </si>
   <si>
     <t>Alteração APOIO Custeio Fundição</t>
   </si>
   <si>
-    <t>23301</t>
+    <t>20/11/2023</t>
+  </si>
+  <si>
+    <t>5531858488</t>
   </si>
   <si>
     <t>Atualizar número da Invoice no documento Benner</t>
   </si>
   <si>
-    <t>22015</t>
+    <t>5540785682</t>
   </si>
   <si>
     <t>Relatório Faturamento: “Relatórios &gt; Saldo do Estoque no Depósito Fabril por Modelo (copy)</t>
   </si>
   <si>
-    <t>20/11/2023</t>
-  </si>
-  <si>
-    <t>22014</t>
+    <t>5540002978</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -171,10 +183,13 @@
     <t>Preparar ambiente de homologação NIMBI</t>
   </si>
   <si>
+    <t>5540785653</t>
+  </si>
+  <si>
     <t>Relatório PCP: “Saldo de Peças por Setor</t>
   </si>
   <si>
-    <t>23014</t>
+    <t>5443725650</t>
   </si>
   <si>
     <t>WMS - Logística interna 3</t>
@@ -183,10 +198,13 @@
     <t>02/11/2023</t>
   </si>
   <si>
+    <t>04/12/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
-    <t>17124</t>
+    <t>3508737415</t>
   </si>
   <si>
     <t>Novo Recurso</t>
@@ -201,16 +219,22 @@
     <t>10/11/2022</t>
   </si>
   <si>
+    <t>27/11/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>23169</t>
+    <t>5532823152</t>
   </si>
   <si>
     <t>Editar Romaneio - Expedição</t>
   </si>
   <si>
-    <t>21456</t>
+    <t>23/11/2023</t>
+  </si>
+  <si>
+    <t>4890467962</t>
   </si>
   <si>
     <t>Melhoria do sistema de alteração de apontamento eletrônico</t>
@@ -222,175 +246,178 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>23151</t>
+    <t>5532840027</t>
   </si>
   <si>
     <t>Grupo de etapa errado</t>
   </si>
   <si>
-    <t>23146</t>
+    <t>5532847596</t>
   </si>
   <si>
     <t>Exclusão de Ordens Preventivas canceladas</t>
   </si>
   <si>
-    <t>23288</t>
+    <t>5531912438</t>
   </si>
   <si>
     <t>Estratificação de dados - Acabamento Komatsu</t>
   </si>
   <si>
-    <t>23117</t>
+    <t>5532859772</t>
   </si>
   <si>
     <t>Saldo de Estoque de Materiais</t>
   </si>
   <si>
-    <t>23283</t>
+    <t>5531931067</t>
   </si>
   <si>
     <t>Fornos inativos</t>
   </si>
   <si>
-    <t>23282</t>
+    <t>5531939922</t>
   </si>
   <si>
     <t>Separar campos no Cadastro de corridas</t>
   </si>
   <si>
-    <t>22957</t>
+    <t>5532881101</t>
   </si>
   <si>
     <t>Data de carteira no relatório do acabamento</t>
   </si>
   <si>
-    <t>23281</t>
+    <t>5531951095</t>
   </si>
   <si>
     <t>CASE no Cadastro de corridas</t>
   </si>
   <si>
-    <t>23274</t>
+    <t>5531959008</t>
   </si>
   <si>
     <t>Fechamento Outubro de 2023</t>
   </si>
   <si>
-    <t>22838</t>
+    <t>5533633087</t>
   </si>
   <si>
     <t>Visualização de Temperaturas no Roteiro para Cadastros exclusivos</t>
   </si>
   <si>
-    <t>23272</t>
+    <t>5532654430</t>
   </si>
   <si>
     <t>Saldo Dep Nac. e Export. no Planilhão</t>
   </si>
   <si>
-    <t>22764</t>
+    <t>5539894792</t>
   </si>
   <si>
     <t>Impressora Zebra  - Homologação</t>
   </si>
   <si>
-    <t>23219</t>
+    <t>5532674726</t>
   </si>
   <si>
     <t>Visualização programação de vazamento</t>
   </si>
   <si>
-    <t>22843</t>
+    <t>5539929529</t>
   </si>
   <si>
     <t>Alteração relatório de invoices</t>
   </si>
   <si>
-    <t>23209</t>
+    <t>5532688513</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || PIS e Cofins sobre Frete da Nota</t>
   </si>
   <si>
-    <t>23160</t>
+    <t>5532831735</t>
   </si>
   <si>
     <t>Gerar PDF a partir do ZPL de impressão Zebra</t>
   </si>
   <si>
-    <t>23179</t>
+    <t>5532776433</t>
   </si>
   <si>
     <t>Ticket para a alteração dos titulos</t>
   </si>
   <si>
-    <t>23290</t>
+    <t>5531868083</t>
   </si>
   <si>
     <t>Relat. Saldo Dep (Nac. e Export.)</t>
   </si>
   <si>
-    <t>23188</t>
+    <t>5532763030</t>
   </si>
   <si>
     <t>BLOQUEIO SEM OTF DE CONJUNTO</t>
   </si>
   <si>
-    <t>23206</t>
+    <t>5532752898</t>
   </si>
   <si>
     <t>Status - Expedição</t>
   </si>
   <si>
-    <t>23173</t>
+    <t>01/12/2023</t>
+  </si>
+  <si>
+    <t>5532803276</t>
   </si>
   <si>
     <t>Inventário BOX - Expedição</t>
   </si>
   <si>
-    <t>23042</t>
+    <t>5443551240</t>
   </si>
   <si>
     <t>POSTO DE CÓPIAS ELETRÔNICO / BLOQUEIO BROWSER (SALVAR COMO / IMPRIMIR)</t>
   </si>
   <si>
-    <t>22695</t>
+    <t>5550387019</t>
   </si>
   <si>
     <t>Filtrar o gráfico de acordo com os dados da tabela</t>
   </si>
   <si>
-    <t>23102</t>
+    <t>5550557995</t>
   </si>
   <si>
     <t>FILTROS DE CONSULTA DIVERSOS DO CPP - Campos a serem adicionados</t>
   </si>
   <si>
+    <t>5550577418</t>
+  </si>
+  <si>
     <t>FILTROS DE CONSULTA DIVERSOS DO CPP - Acrescentar + de um campo p/ o mesmo filtro</t>
   </si>
   <si>
-    <t>22647</t>
+    <t>5561710704</t>
   </si>
   <si>
     <t>Inativar responsável no controle de refugo</t>
   </si>
   <si>
-    <t>23/11/2023</t>
-  </si>
-  <si>
-    <t>23314</t>
+    <t>5532905586</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - Inspeção da Qualidade</t>
   </si>
   <si>
-    <t>23207</t>
+    <t>5532726394</t>
   </si>
   <si>
     <t>Melhorias e Alterações - Controle na moldagem + planilhão</t>
   </si>
   <si>
-    <t>23145</t>
+    <t>5532852645</t>
   </si>
   <si>
     <t>E-mails automáticos - Sistema de desmoldagem</t>
@@ -402,7 +429,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-24</t>
+    <t>Nov/2022</t>
   </si>
   <si>
     <t>Base</t>
@@ -472,6 +499,9 @@
   </si>
   <si>
     <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -1141,7 +1171,7 @@
         <v>35</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1158,38 +1188,38 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1197,7 +1227,7 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1205,7 +1235,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1217,34 +1247,34 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1252,7 +1282,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1264,10 +1294,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -1279,10 +1309,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1291,7 +1321,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1299,7 +1329,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1311,10 +1341,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -1329,7 +1359,7 @@
         <v>35</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1346,7 +1376,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1358,10 +1388,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -1376,7 +1406,7 @@
         <v>35</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1393,7 +1423,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1405,10 +1435,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -1423,7 +1453,7 @@
         <v>48</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1440,22 +1470,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -1470,7 +1500,7 @@
         <v>48</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1487,7 +1517,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1499,10 +1529,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -1517,7 +1547,7 @@
         <v>48</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1534,7 +1564,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1546,10 +1576,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -1561,10 +1591,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1573,7 +1603,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1581,25 +1611,25 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1608,10 +1638,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1620,7 +1650,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1628,7 +1658,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1640,10 +1670,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -1658,7 +1688,7 @@
         <v>35</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1675,7 +1705,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1687,10 +1717,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -1702,10 +1732,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1714,15 +1744,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1734,10 +1764,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -1752,7 +1782,7 @@
         <v>35</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1769,7 +1799,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1781,10 +1811,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -1799,7 +1829,7 @@
         <v>35</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1816,7 +1846,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1828,10 +1858,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -1846,7 +1876,7 @@
         <v>35</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1863,7 +1893,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1875,10 +1905,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -1893,7 +1923,7 @@
         <v>35</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1910,7 +1940,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1922,10 +1952,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -1940,7 +1970,7 @@
         <v>35</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1957,7 +1987,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1969,10 +1999,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -1987,7 +2017,7 @@
         <v>35</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2004,7 +2034,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2016,10 +2046,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -2034,7 +2064,7 @@
         <v>35</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2051,7 +2081,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2063,10 +2093,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -2081,7 +2111,7 @@
         <v>35</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2098,7 +2128,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2110,10 +2140,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -2128,7 +2158,7 @@
         <v>35</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2145,7 +2175,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2157,10 +2187,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -2175,7 +2205,7 @@
         <v>35</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2192,7 +2222,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2204,10 +2234,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -2222,7 +2252,7 @@
         <v>35</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2239,7 +2269,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2251,10 +2281,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -2269,7 +2299,7 @@
         <v>48</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2286,7 +2316,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2298,10 +2328,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
@@ -2316,7 +2346,7 @@
         <v>35</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2333,7 +2363,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2345,10 +2375,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
@@ -2363,7 +2393,7 @@
         <v>48</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2380,7 +2410,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2392,10 +2422,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>34</v>
@@ -2410,7 +2440,7 @@
         <v>35</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2427,7 +2457,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2439,10 +2469,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
@@ -2457,7 +2487,7 @@
         <v>35</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2474,7 +2504,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2486,10 +2516,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>34</v>
@@ -2504,7 +2534,7 @@
         <v>35</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2521,7 +2551,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2533,10 +2563,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>34</v>
@@ -2551,7 +2581,7 @@
         <v>35</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2568,7 +2598,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2580,10 +2610,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>34</v>
@@ -2598,7 +2628,7 @@
         <v>35</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2615,7 +2645,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2627,10 +2657,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>34</v>
@@ -2645,7 +2675,7 @@
         <v>35</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2662,7 +2692,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2674,10 +2704,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>34</v>
@@ -2692,7 +2722,7 @@
         <v>35</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2709,7 +2739,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2721,10 +2751,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>34</v>
@@ -2736,10 +2766,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2748,7 +2778,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -2756,7 +2786,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2768,10 +2798,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>34</v>
@@ -2786,7 +2816,7 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2803,7 +2833,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2815,10 +2845,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>34</v>
@@ -2833,7 +2863,7 @@
         <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2850,7 +2880,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2862,10 +2892,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>34</v>
@@ -2880,7 +2910,7 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2897,7 +2927,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2909,10 +2939,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>34</v>
@@ -2924,10 +2954,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2936,7 +2966,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -2944,7 +2974,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -2956,10 +2986,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>34</v>
@@ -2974,7 +3004,7 @@
         <v>35</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -2991,7 +3021,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3003,10 +3033,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>34</v>
@@ -3021,7 +3051,7 @@
         <v>35</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3038,7 +3068,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3050,10 +3080,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>34</v>
@@ -3068,7 +3098,7 @@
         <v>35</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3096,23 +3126,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3120,16 +3150,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3140,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>20.84</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3148,7 +3178,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3161,7 +3191,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3169,7 +3199,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3200,12 +3230,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B2">
         <v>45</v>
@@ -3219,7 +3249,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3229,25 +3259,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3264,13 +3294,13 @@
         <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3282,10 +3312,10 @@
         <v>45</v>
       </c>
       <c r="P10" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -3296,7 +3326,7 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -3308,21 +3338,21 @@
         <v>45</v>
       </c>
       <c r="M11" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3334,48 +3364,48 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="Q12">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="Q13">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
@@ -3386,7 +3416,7 @@
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3394,7 +3424,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3402,7 +3432,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3410,7 +3440,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3418,10 +3448,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3429,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3437,142 +3467,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>19</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
